--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860497</v>
+        <v>122860460</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589009</v>
+        <v>589028</v>
       </c>
       <c r="R3" t="n">
-        <v>7049395</v>
+        <v>7049424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122860460</v>
+        <v>122860281</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589028</v>
+        <v>588960</v>
       </c>
       <c r="R4" t="n">
-        <v>7049424</v>
+        <v>7049462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860281</v>
+        <v>122860497</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588960</v>
+        <v>589009</v>
       </c>
       <c r="R5" t="n">
-        <v>7049462</v>
+        <v>7049395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,12 +1111,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122860415</v>
+        <v>122860497</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589026</v>
+        <v>589009</v>
       </c>
       <c r="R2" t="n">
-        <v>7049501</v>
+        <v>7049395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860460</v>
+        <v>122860281</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589028</v>
+        <v>588960</v>
       </c>
       <c r="R3" t="n">
-        <v>7049424</v>
+        <v>7049462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +887,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122860281</v>
+        <v>122860460</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588960</v>
+        <v>589028</v>
       </c>
       <c r="R4" t="n">
-        <v>7049462</v>
+        <v>7049424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860497</v>
+        <v>122860595</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589009</v>
+        <v>589004</v>
       </c>
       <c r="R5" t="n">
-        <v>7049395</v>
+        <v>7049361</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122860595</v>
+        <v>122860415</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589004</v>
+        <v>589026</v>
       </c>
       <c r="R6" t="n">
-        <v>7049361</v>
+        <v>7049501</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122860497</v>
+        <v>122860460</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589009</v>
+        <v>589028</v>
       </c>
       <c r="R2" t="n">
-        <v>7049395</v>
+        <v>7049424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860281</v>
+        <v>122860595</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588960</v>
+        <v>589004</v>
       </c>
       <c r="R3" t="n">
-        <v>7049462</v>
+        <v>7049361</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122860460</v>
+        <v>122860281</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -939,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589028</v>
+        <v>588960</v>
       </c>
       <c r="R4" t="n">
-        <v>7049424</v>
+        <v>7049462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860595</v>
+        <v>122860497</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589004</v>
+        <v>589009</v>
       </c>
       <c r="R5" t="n">
-        <v>7049361</v>
+        <v>7049395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,12 +1121,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122860460</v>
+        <v>122860497</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589028</v>
+        <v>589009</v>
       </c>
       <c r="R2" t="n">
-        <v>7049424</v>
+        <v>7049395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860595</v>
+        <v>122860281</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589004</v>
+        <v>588960</v>
       </c>
       <c r="R3" t="n">
-        <v>7049361</v>
+        <v>7049462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122860281</v>
+        <v>122860415</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588960</v>
+        <v>589026</v>
       </c>
       <c r="R4" t="n">
-        <v>7049462</v>
+        <v>7049501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860497</v>
+        <v>122860460</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1061,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589009</v>
+        <v>589028</v>
       </c>
       <c r="R5" t="n">
-        <v>7049395</v>
+        <v>7049424</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122860415</v>
+        <v>122860595</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589026</v>
+        <v>589004</v>
       </c>
       <c r="R6" t="n">
-        <v>7049501</v>
+        <v>7049361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122860497</v>
+        <v>122860460</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589009</v>
+        <v>589028</v>
       </c>
       <c r="R2" t="n">
-        <v>7049395</v>
+        <v>7049424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860281</v>
+        <v>122860497</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588960</v>
+        <v>589009</v>
       </c>
       <c r="R3" t="n">
-        <v>7049462</v>
+        <v>7049395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +887,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122860415</v>
+        <v>122860281</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589026</v>
+        <v>588960</v>
       </c>
       <c r="R4" t="n">
-        <v>7049501</v>
+        <v>7049462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860460</v>
+        <v>122860415</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589028</v>
+        <v>589026</v>
       </c>
       <c r="R5" t="n">
-        <v>7049424</v>
+        <v>7049501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122860460</v>
+        <v>122860595</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589028</v>
+        <v>589004</v>
       </c>
       <c r="R2" t="n">
-        <v>7049424</v>
+        <v>7049361</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +785,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860497</v>
+        <v>122860415</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589009</v>
+        <v>589026</v>
       </c>
       <c r="R3" t="n">
-        <v>7049395</v>
+        <v>7049501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122860281</v>
+        <v>122860460</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -939,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588960</v>
+        <v>589028</v>
       </c>
       <c r="R4" t="n">
-        <v>7049462</v>
+        <v>7049424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +1009,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860415</v>
+        <v>122860497</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1051,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589026</v>
+        <v>589009</v>
       </c>
       <c r="R5" t="n">
-        <v>7049501</v>
+        <v>7049395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122860595</v>
+        <v>122860281</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589004</v>
+        <v>588960</v>
       </c>
       <c r="R6" t="n">
-        <v>7049361</v>
+        <v>7049462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122860595</v>
+        <v>122860415</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589004</v>
+        <v>589026</v>
       </c>
       <c r="R2" t="n">
-        <v>7049361</v>
+        <v>7049501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860415</v>
+        <v>122860460</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589026</v>
+        <v>589028</v>
       </c>
       <c r="R3" t="n">
-        <v>7049501</v>
+        <v>7049424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122860460</v>
+        <v>122860497</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589028</v>
+        <v>589009</v>
       </c>
       <c r="R4" t="n">
-        <v>7049424</v>
+        <v>7049395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860497</v>
+        <v>122860595</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589009</v>
+        <v>589004</v>
       </c>
       <c r="R5" t="n">
-        <v>7049395</v>
+        <v>7049361</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,12 +1121,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122860415</v>
+        <v>122860460</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589026</v>
+        <v>589028</v>
       </c>
       <c r="R2" t="n">
-        <v>7049501</v>
+        <v>7049424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860460</v>
+        <v>122860281</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589028</v>
+        <v>588960</v>
       </c>
       <c r="R3" t="n">
-        <v>7049424</v>
+        <v>7049462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,7 +902,7 @@
         <v>122860497</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860595</v>
+        <v>122860415</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589004</v>
+        <v>589026</v>
       </c>
       <c r="R5" t="n">
-        <v>7049361</v>
+        <v>7049501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122860281</v>
+        <v>122860595</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588960</v>
+        <v>589004</v>
       </c>
       <c r="R6" t="n">
-        <v>7049462</v>
+        <v>7049361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122860460</v>
+        <v>122860415</v>
       </c>
       <c r="B2" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589028</v>
+        <v>589026</v>
       </c>
       <c r="R2" t="n">
-        <v>7049424</v>
+        <v>7049501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860281</v>
+        <v>122860595</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588960</v>
+        <v>589004</v>
       </c>
       <c r="R3" t="n">
-        <v>7049462</v>
+        <v>7049361</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +912,7 @@
         <v>122860497</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860415</v>
+        <v>122860281</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589026</v>
+        <v>588960</v>
       </c>
       <c r="R5" t="n">
-        <v>7049501</v>
+        <v>7049462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122860595</v>
+        <v>122860460</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589004</v>
+        <v>589028</v>
       </c>
       <c r="R6" t="n">
-        <v>7049361</v>
+        <v>7049424</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 5247-2025 artfynd.xlsx
+++ b/artfynd/A 5247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122860415</v>
+        <v>122860595</v>
       </c>
       <c r="B2" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589026</v>
+        <v>589004</v>
       </c>
       <c r="R2" t="n">
-        <v>7049501</v>
+        <v>7049361</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122860595</v>
+        <v>122860415</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589004</v>
+        <v>589026</v>
       </c>
       <c r="R3" t="n">
-        <v>7049361</v>
+        <v>7049501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122860497</v>
+        <v>122860281</v>
       </c>
       <c r="B4" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589009</v>
+        <v>588960</v>
       </c>
       <c r="R4" t="n">
-        <v>7049395</v>
+        <v>7049462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122860281</v>
+        <v>122860497</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588960</v>
+        <v>589009</v>
       </c>
       <c r="R5" t="n">
-        <v>7049462</v>
+        <v>7049395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,12 +1121,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
         <v>122860460</v>
       </c>
       <c r="B6" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
